--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B88A92C-F856-45D6-8CA9-B0D6CA781CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA6D965-D5FA-4E47-86DB-007938EB7D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DD97EB0-B1FD-49CB-A9AD-A3F04F28C9FE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="126">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -156,10 +156,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Material</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Emotion</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -224,32 +220,12 @@
     <t>辩证法</t>
   </si>
   <si>
-    <t>辩证法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>谜</t>
   </si>
   <si>
-    <t>谜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>沙漠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冻土</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>罪</t>
   </si>
   <si>
-    <t>罪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>f8</t>
   </si>
   <si>
@@ -265,10 +241,6 @@
     <t>f13</t>
   </si>
   <si>
-    <t>Universal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Forge_Index</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -459,58 +431,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>火</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>空气</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>世界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>熵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>理性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帝国</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奇迹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>零</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>n1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -536,6 +456,26 @@
   </si>
   <si>
     <t>e3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f8,f22,f25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f10,f27,f20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f9,f28,f21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烦躁</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -663,7 +603,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -694,19 +634,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1023,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC2FDD69-928B-4F19-A695-2238DDC39BD8}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1052,7 +980,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>14</v>
@@ -1069,10 +997,10 @@
         <v>28</v>
       </c>
       <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
         <v>33</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -1086,13 +1014,13 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3">
         <v>-2</v>
@@ -1103,13 +1031,13 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1117,36 +1045,36 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -1154,16 +1082,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -1171,16 +1099,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -1188,16 +1116,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -1205,254 +1133,106 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="F10" t="s">
-        <v>62</v>
+      <c r="E10">
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>98</v>
       </c>
-      <c r="B16" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>99</v>
       </c>
-      <c r="B17" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>100</v>
-      </c>
-      <c r="B18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>103</v>
       </c>
-      <c r="B21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>104</v>
       </c>
-      <c r="B22" t="s">
-        <v>131</v>
-      </c>
-      <c r="C22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>105</v>
       </c>
-      <c r="B23" t="s">
-        <v>132</v>
-      </c>
-      <c r="C23" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>110</v>
-      </c>
-      <c r="B25" t="s">
-        <v>133</v>
-      </c>
-      <c r="C25" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1509,7 +1289,7 @@
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -1574,13 +1354,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -1591,13 +1371,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -1608,13 +1388,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -1631,519 +1411,501 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B253778A-ACB1-4C24-B0F9-D46A0ADE082F}">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" t="s">
         <v>78</v>
       </c>
-      <c r="D1" t="s">
+      <c r="J1" t="s">
         <v>79</v>
       </c>
-      <c r="E1" t="s">
+      <c r="K1" t="s">
         <v>80</v>
       </c>
-      <c r="F1" t="s">
+      <c r="L1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M1" t="s">
         <v>82</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" t="s">
         <v>83</v>
       </c>
-      <c r="H1" t="s">
+      <c r="O1" t="s">
         <v>84</v>
       </c>
-      <c r="I1" t="s">
+      <c r="P1" t="s">
         <v>85</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
         <v>86</v>
       </c>
-      <c r="K1" t="s">
+      <c r="R1" t="s">
         <v>87</v>
-      </c>
-      <c r="L1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N1" t="s">
-        <v>90</v>
-      </c>
-      <c r="O1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P1" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>93</v>
-      </c>
-      <c r="R1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="M2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="P2" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="Q2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="11"/>
+        <v>58</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="7"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="7"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="11"/>
+        <v>60</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="7"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="11"/>
+        <v>61</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="7"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="11"/>
+        <v>62</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="7"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="11"/>
+        <v>63</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="7"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="11"/>
+        <v>64</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="7"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="11"/>
+        <v>65</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="7"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="11"/>
+        <v>66</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="7"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
+        <v>67</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="11"/>
+        <v>50</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="7"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="11"/>
+        <v>49</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="7"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="11"/>
+        <v>68</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="7"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="11"/>
+        <v>69</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="7"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
+        <v>48</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
+        <v>70</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2159,21 +1921,21 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="D1" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="E1" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -2181,17 +1943,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2207,21 +1969,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="D1" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="E1" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -2229,17 +1991,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2255,7 +2017,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
         <v>18</v>
@@ -2264,12 +2026,12 @@
         <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -2287,7 +2049,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA6D965-D5FA-4E47-86DB-007938EB7D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBE3FD6-C36A-4C6F-99DC-F45BC54D0174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DD97EB0-B1FD-49CB-A9AD-A3F04F28C9FE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="108">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -235,12 +235,6 @@
     <t>f11</t>
   </si>
   <si>
-    <t>f12</t>
-  </si>
-  <si>
-    <t>f13</t>
-  </si>
-  <si>
     <t>Forge_Index</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -342,42 +336,6 @@
     <t>u16</t>
   </si>
   <si>
-    <t>f14</t>
-  </si>
-  <si>
-    <t>f15</t>
-  </si>
-  <si>
-    <t>f16</t>
-  </si>
-  <si>
-    <t>f17</t>
-  </si>
-  <si>
-    <t>f18</t>
-  </si>
-  <si>
-    <t>f19</t>
-  </si>
-  <si>
-    <t>f20</t>
-  </si>
-  <si>
-    <t>f21</t>
-  </si>
-  <si>
-    <t>f22</t>
-  </si>
-  <si>
-    <t>f23</t>
-  </si>
-  <si>
-    <t>f24</t>
-  </si>
-  <si>
-    <t>f25</t>
-  </si>
-  <si>
     <t>PainTest</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -390,15 +348,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>f26</t>
-  </si>
-  <si>
-    <t>f27</t>
-  </si>
-  <si>
-    <t>f28</t>
-  </si>
-  <si>
     <t>哲学学位</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -468,10 +417,6 @@
   </si>
   <si>
     <t>f9,f28,f21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f29</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -951,7 +896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC2FDD69-928B-4F19-A695-2238DDC39BD8}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1014,7 +959,7 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
         <v>31</v>
@@ -1031,7 +976,7 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
@@ -1048,7 +993,7 @@
         <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
@@ -1068,7 +1013,7 @@
         <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
@@ -1085,7 +1030,7 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -1099,10 +1044,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
@@ -1119,7 +1064,7 @@
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
@@ -1136,103 +1081,13 @@
         <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
       </c>
       <c r="E10">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1289,7 +1144,7 @@
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -1357,10 +1212,10 @@
         <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -1374,10 +1229,10 @@
         <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -1391,10 +1246,10 @@
         <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -1416,93 +1271,93 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>73</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>76</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>77</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>78</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>79</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>80</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>81</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>82</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>83</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>84</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>85</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>86</v>
-      </c>
-      <c r="R1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="L2" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="M2" s="7" t="s">
         <v>50</v>
@@ -1511,24 +1366,24 @@
         <v>49</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q2" s="8" t="s">
         <v>48</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -1549,10 +1404,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -1573,10 +1428,10 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -1597,10 +1452,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -1621,10 +1476,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1645,10 +1500,10 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1669,10 +1524,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1693,10 +1548,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -1717,10 +1572,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -1741,10 +1596,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -1765,7 +1620,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>50</v>
@@ -1789,7 +1644,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>49</v>
@@ -1813,10 +1668,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -1837,10 +1692,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1861,7 +1716,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>48</v>
@@ -1885,10 +1740,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1921,21 +1776,21 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E1" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -1943,17 +1798,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1969,21 +1824,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="E1" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -1991,17 +1846,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2017,7 +1872,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
         <v>18</v>
@@ -2026,12 +1881,12 @@
         <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -2049,7 +1904,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBE3FD6-C36A-4C6F-99DC-F45BC54D0174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EF3DC0-43D3-49A3-984B-38A02BD30F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DD97EB0-B1FD-49CB-A9AD-A3F04F28C9FE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DD97EB0-B1FD-49CB-A9AD-A3F04F28C9FE}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="176">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -182,246 +182,461 @@
     <t>f6</t>
   </si>
   <si>
+    <t>c5,c6,c7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c5</t>
+  </si>
+  <si>
+    <t>c6</t>
+  </si>
+  <si>
+    <t>c7</t>
+  </si>
+  <si>
+    <t>一份勉强能糊口的编剧工作，为一部庸俗短片攥写剧本。</t>
+  </si>
+  <si>
+    <t>你花了四年时间研究俄罗斯文学，你能熟练解释东正教传统和未来主义在白银时代的演变。\n显然这对找到一份工作没有什么帮助。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的大学文凭，全世界最没用的东西\n你学的是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你花了四年时间研究黎巴嫩的近代历史，你能熟练叙述宗教冲突如何塑造这个国家里不同阶级的身份认同。\n显然这对找到一份工作没有什么帮助。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。\n显然这对找到一份工作没有什么帮助。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辩证法</t>
+  </si>
+  <si>
+    <t>谜</t>
+  </si>
+  <si>
+    <t>罪</t>
+  </si>
+  <si>
+    <t>f8</t>
+  </si>
+  <si>
+    <t>f10</t>
+  </si>
+  <si>
+    <t>f11</t>
+  </si>
+  <si>
+    <t>Forge_Index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>冬</t>
+  </si>
+  <si>
+    <t>铁</t>
+  </si>
+  <si>
+    <t>空气</t>
+  </si>
+  <si>
+    <t>世界</t>
+  </si>
+  <si>
+    <t>大地</t>
+  </si>
+  <si>
+    <t>熵</t>
+  </si>
+  <si>
+    <t>死亡</t>
+  </si>
+  <si>
+    <t>理性</t>
+  </si>
+  <si>
+    <t>帝国</t>
+  </si>
+  <si>
+    <t>奇迹</t>
+  </si>
+  <si>
+    <t>爱</t>
+  </si>
+  <si>
+    <t>零</t>
+  </si>
+  <si>
+    <t>u1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u3</t>
+  </si>
+  <si>
+    <t>u3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u4</t>
+  </si>
+  <si>
+    <t>u5</t>
+  </si>
+  <si>
+    <t>u6</t>
+  </si>
+  <si>
+    <t>u7</t>
+  </si>
+  <si>
+    <t>u8</t>
+  </si>
+  <si>
+    <t>u9</t>
+  </si>
+  <si>
+    <t>u10</t>
+  </si>
+  <si>
+    <t>u11</t>
+  </si>
+  <si>
+    <t>u12</t>
+  </si>
+  <si>
+    <t>u13</t>
+  </si>
+  <si>
+    <t>u14</t>
+  </si>
+  <si>
+    <t>u15</t>
+  </si>
+  <si>
+    <t>u16</t>
+  </si>
+  <si>
+    <t>PainTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HapinessTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f2,f3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲学学位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比较文学学位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社会学学位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的文凭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社会学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比较文学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>p1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>p2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>p3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>e3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烦躁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>f7</t>
-  </si>
-  <si>
-    <t>c5,c6,c7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c5</t>
-  </si>
-  <si>
-    <t>c6</t>
-  </si>
-  <si>
-    <t>c7</t>
-  </si>
-  <si>
-    <t>一份勉强能糊口的编剧工作，为一部庸俗短片攥写剧本。</t>
-  </si>
-  <si>
-    <t>你花了四年时间研究俄罗斯文学，你能熟练解释东正教传统和未来主义在白银时代的演变。\n显然这对找到一份工作没有什么帮助。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的大学文凭，全世界最没用的东西\n你学的是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你花了四年时间研究黎巴嫩的近代历史，你能熟练叙述宗教冲突如何塑造这个国家里不同阶级的身份认同。\n显然这对找到一份工作没有什么帮助。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。\n显然这对找到一份工作没有什么帮助。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f12</t>
+  </si>
+  <si>
+    <t>f13</t>
+  </si>
+  <si>
+    <t>f14</t>
+  </si>
+  <si>
+    <t>f15</t>
+  </si>
+  <si>
+    <t>f16</t>
+  </si>
+  <si>
+    <t>f17</t>
   </si>
   <si>
     <t>辩证法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Universal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>谜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙漠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战争</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冻土</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>罪</t>
-  </si>
-  <si>
-    <t>f8</t>
-  </si>
-  <si>
-    <t>f10</t>
-  </si>
-  <si>
-    <t>f11</t>
-  </si>
-  <si>
-    <t>Forge_Index</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火</t>
-  </si>
-  <si>
-    <t>冬</t>
-  </si>
-  <si>
-    <t>铁</t>
-  </si>
-  <si>
-    <t>空气</t>
-  </si>
-  <si>
-    <t>世界</t>
-  </si>
-  <si>
-    <t>大地</t>
-  </si>
-  <si>
-    <t>熵</t>
-  </si>
-  <si>
-    <t>死亡</t>
-  </si>
-  <si>
-    <t>理性</t>
-  </si>
-  <si>
-    <t>帝国</t>
-  </si>
-  <si>
-    <t>奇迹</t>
-  </si>
-  <si>
-    <t>爱</t>
-  </si>
-  <si>
-    <t>零</t>
-  </si>
-  <si>
-    <t>u1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u3</t>
-  </si>
-  <si>
-    <t>u3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u4</t>
-  </si>
-  <si>
-    <t>u5</t>
-  </si>
-  <si>
-    <t>u6</t>
-  </si>
-  <si>
-    <t>u7</t>
-  </si>
-  <si>
-    <t>u8</t>
-  </si>
-  <si>
-    <t>u9</t>
-  </si>
-  <si>
-    <t>u10</t>
-  </si>
-  <si>
-    <t>u11</t>
-  </si>
-  <si>
-    <t>u12</t>
-  </si>
-  <si>
-    <t>u13</t>
-  </si>
-  <si>
-    <t>u14</t>
-  </si>
-  <si>
-    <t>u15</t>
-  </si>
-  <si>
-    <t>u16</t>
-  </si>
-  <si>
-    <t>PainTest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HapinessTest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f2,f3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲学学位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比较文学学位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>社会学学位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的工作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的文凭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>社会学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比较文学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>n1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>n2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>n3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>p1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>p2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>p3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>e3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f8,f22,f25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f10,f27,f20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f9,f28,f21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>烦躁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Politics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f12,f13,f8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f14,f15,f9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f16,f17,f10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岛</t>
+  </si>
+  <si>
+    <t>n4</t>
+  </si>
+  <si>
+    <t>n5</t>
+  </si>
+  <si>
+    <t>n6</t>
+  </si>
+  <si>
+    <t>n7</t>
+  </si>
+  <si>
+    <t>平原</t>
+  </si>
+  <si>
+    <t>海</t>
+  </si>
+  <si>
+    <t>高原</t>
+  </si>
+  <si>
+    <t>山</t>
+  </si>
+  <si>
+    <t>大陆</t>
+  </si>
+  <si>
+    <t>荒原</t>
+  </si>
+  <si>
+    <t>丛林</t>
+  </si>
+  <si>
+    <t>城市</t>
+  </si>
+  <si>
+    <t>n8</t>
+  </si>
+  <si>
+    <t>n9</t>
+  </si>
+  <si>
+    <t>n10</t>
+  </si>
+  <si>
+    <t>n11</t>
+  </si>
+  <si>
+    <t>n12</t>
+  </si>
+  <si>
+    <t>n13</t>
+  </si>
+  <si>
+    <t>n14</t>
+  </si>
+  <si>
+    <t>n15</t>
+  </si>
+  <si>
+    <t>n16</t>
+  </si>
+  <si>
+    <t>n17</t>
+  </si>
+  <si>
+    <t>n18</t>
+  </si>
+  <si>
+    <t>n19</t>
+  </si>
+  <si>
+    <t>n20</t>
+  </si>
+  <si>
+    <t>n21</t>
+  </si>
+  <si>
+    <t>n22</t>
+  </si>
+  <si>
+    <t>n23</t>
+  </si>
+  <si>
+    <t>n24</t>
+  </si>
+  <si>
+    <t>n25</t>
+  </si>
+  <si>
+    <t>n26</t>
+  </si>
+  <si>
+    <t>n27</t>
+  </si>
+  <si>
+    <t>f18</t>
+  </si>
+  <si>
+    <t>f19</t>
+  </si>
+  <si>
+    <t>f20</t>
+  </si>
+  <si>
+    <t>f21</t>
+  </si>
+  <si>
+    <t>f22</t>
+  </si>
+  <si>
+    <t>f23</t>
+  </si>
+  <si>
+    <t>f24</t>
+  </si>
+  <si>
+    <t>f25</t>
+  </si>
+  <si>
+    <t>f26</t>
+  </si>
+  <si>
+    <t>f27</t>
+  </si>
+  <si>
+    <t>f28</t>
+  </si>
+  <si>
+    <t>f29</t>
+  </si>
+  <si>
+    <t>f30</t>
+  </si>
+  <si>
+    <t>f31</t>
+  </si>
+  <si>
+    <t>f32</t>
+  </si>
+  <si>
+    <t>f33</t>
+  </si>
+  <si>
+    <t>f34</t>
+  </si>
+  <si>
+    <t>f35</t>
+  </si>
+  <si>
+    <t>f36</t>
   </si>
 </sst>
 </file>
@@ -478,7 +693,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,6 +715,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3D600"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,7 +769,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -581,6 +802,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -896,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC2FDD69-928B-4F19-A695-2238DDC39BD8}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -959,7 +1183,7 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
         <v>31</v>
@@ -976,7 +1200,7 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
@@ -993,33 +1217,33 @@
         <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -1027,16 +1251,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -1044,16 +1268,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -1061,16 +1285,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -1078,16 +1302,198 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
       </c>
       <c r="E10">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -1144,7 +1550,7 @@
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -1209,13 +1615,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -1226,13 +1632,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -1243,13 +1649,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -1271,119 +1677,119 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" t="s">
         <v>69</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>70</v>
       </c>
-      <c r="E1" t="s">
-        <v>71</v>
-      </c>
       <c r="F1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" t="s">
         <v>73</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>74</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>75</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>76</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>77</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>78</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>79</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>80</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>81</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>82</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>83</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>84</v>
-      </c>
-      <c r="R1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="M2" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="O2" s="7" t="s">
+      <c r="P2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="Q2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -1404,10 +1810,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -1428,10 +1834,10 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -1452,10 +1858,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -1476,10 +1882,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1500,10 +1906,10 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1524,10 +1930,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1548,10 +1954,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -1572,10 +1978,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -1596,10 +2002,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -1620,10 +2026,10 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -1644,10 +2050,10 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -1668,10 +2074,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -1692,10 +2098,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1716,10 +2122,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -1740,10 +2146,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1770,45 +2176,303 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{605FD685-18E4-4B72-A885-1B914A54470F}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" t="s">
         <v>97</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>98</v>
       </c>
-      <c r="E1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J1" t="s">
+        <v>137</v>
+      </c>
+      <c r="K1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L1" t="s">
+        <v>139</v>
+      </c>
+      <c r="M1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="B4" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>99</v>
+      <c r="B5" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>156</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1824,21 +2488,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" t="s">
         <v>100</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>101</v>
-      </c>
-      <c r="E1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -1846,17 +2510,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1872,7 +2536,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
         <v>18</v>
@@ -1881,12 +2545,12 @@
         <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -1904,7 +2568,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EF3DC0-43D3-49A3-984B-38A02BD30F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E792F9D1-CAFA-45F7-A971-FBDBE08C808E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DD97EB0-B1FD-49CB-A9AD-A3F04F28C9FE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{6DD97EB0-B1FD-49CB-A9AD-A3F04F28C9FE}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="ForgeLibrary_Nature" sheetId="8" r:id="rId4"/>
     <sheet name="ForgeLibrary_Politics" sheetId="9" r:id="rId5"/>
     <sheet name="ForgeLibrary_Emotion" sheetId="7" r:id="rId6"/>
+    <sheet name="Node" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="221">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -82,14 +83,6 @@
     <t>DestroyWhenUsed</t>
   </si>
   <si>
-    <t>c1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Useable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -100,92 +93,20 @@
     <t>c4</t>
   </si>
   <si>
-    <t>c1,c2,c3,c4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>e1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>f1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>e2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>e1 Created</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>e2 Created</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Create Hapiness</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreatePain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HideOther Choice</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Destroy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hided</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmotionCreatorTest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Emotion</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Raw Card Test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Eternal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A mirracle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MaterialType</t>
   </si>
   <si>
     <t>f6</t>
   </si>
   <si>
-    <t>c5,c6,c7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>c5</t>
   </si>
   <si>
@@ -193,25 +114,6 @@
   </si>
   <si>
     <t>c7</t>
-  </si>
-  <si>
-    <t>一份勉强能糊口的编剧工作，为一部庸俗短片攥写剧本。</t>
-  </si>
-  <si>
-    <t>你花了四年时间研究俄罗斯文学，你能熟练解释东正教传统和未来主义在白银时代的演变。\n显然这对找到一份工作没有什么帮助。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的大学文凭，全世界最没用的东西\n你学的是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你花了四年时间研究黎巴嫩的近代历史，你能熟练叙述宗教冲突如何塑造这个国家里不同阶级的身份认同。\n显然这对找到一份工作没有什么帮助。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。\n显然这对找到一份工作没有什么帮助。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>辩证法</t>
@@ -236,10 +138,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>f9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>火</t>
   </si>
   <si>
@@ -333,50 +231,6 @@
     <t>u16</t>
   </si>
   <si>
-    <t>PainTest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HapinessTest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f2,f3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲学学位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比较文学学位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>社会学学位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的工作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的文凭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>社会学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比较文学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>n1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -405,14 +259,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>烦躁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>f12</t>
   </si>
   <si>
@@ -429,214 +275,457 @@
   </si>
   <si>
     <t>f17</t>
-  </si>
-  <si>
-    <t>辩证法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Universal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Material</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>谜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>沙漠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>战争</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>冻土</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>罪</t>
+    <t>岛</t>
+  </si>
+  <si>
+    <t>n4</t>
+  </si>
+  <si>
+    <t>n5</t>
+  </si>
+  <si>
+    <t>n6</t>
+  </si>
+  <si>
+    <t>n7</t>
+  </si>
+  <si>
+    <t>平原</t>
+  </si>
+  <si>
+    <t>海</t>
+  </si>
+  <si>
+    <t>高原</t>
+  </si>
+  <si>
+    <t>山</t>
+  </si>
+  <si>
+    <t>大陆</t>
+  </si>
+  <si>
+    <t>荒原</t>
+  </si>
+  <si>
+    <t>丛林</t>
+  </si>
+  <si>
+    <t>城市</t>
+  </si>
+  <si>
+    <t>n8</t>
+  </si>
+  <si>
+    <t>n9</t>
+  </si>
+  <si>
+    <t>n10</t>
+  </si>
+  <si>
+    <t>n11</t>
+  </si>
+  <si>
+    <t>n12</t>
+  </si>
+  <si>
+    <t>n13</t>
+  </si>
+  <si>
+    <t>n14</t>
+  </si>
+  <si>
+    <t>n15</t>
+  </si>
+  <si>
+    <t>n16</t>
+  </si>
+  <si>
+    <t>n17</t>
+  </si>
+  <si>
+    <t>n18</t>
+  </si>
+  <si>
+    <t>n19</t>
+  </si>
+  <si>
+    <t>n20</t>
+  </si>
+  <si>
+    <t>n21</t>
+  </si>
+  <si>
+    <t>n22</t>
+  </si>
+  <si>
+    <t>n23</t>
+  </si>
+  <si>
+    <t>n24</t>
+  </si>
+  <si>
+    <t>n25</t>
+  </si>
+  <si>
+    <t>n26</t>
+  </si>
+  <si>
+    <t>n27</t>
+  </si>
+  <si>
+    <t>f18</t>
+  </si>
+  <si>
+    <t>f19</t>
+  </si>
+  <si>
+    <t>f20</t>
+  </si>
+  <si>
+    <t>f21</t>
+  </si>
+  <si>
+    <t>f22</t>
+  </si>
+  <si>
+    <t>f23</t>
+  </si>
+  <si>
+    <t>f24</t>
+  </si>
+  <si>
+    <t>f25</t>
+  </si>
+  <si>
+    <t>f26</t>
+  </si>
+  <si>
+    <t>f27</t>
+  </si>
+  <si>
+    <t>f28</t>
+  </si>
+  <si>
+    <t>f29</t>
+  </si>
+  <si>
+    <t>f30</t>
+  </si>
+  <si>
+    <t>f31</t>
+  </si>
+  <si>
+    <t>f32</t>
+  </si>
+  <si>
+    <t>f33</t>
+  </si>
+  <si>
+    <t>f34</t>
+  </si>
+  <si>
+    <t>f35</t>
+  </si>
+  <si>
+    <t>f36</t>
+  </si>
+  <si>
+    <t>RandomCardList</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>RandomCardNumber</t>
+  </si>
+  <si>
+    <t>CanBeDropped</t>
+  </si>
+  <si>
+    <t>TimeConsumed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>Create Hapiness</t>
+  </si>
+  <si>
+    <t>e1 Created</t>
+  </si>
+  <si>
+    <t>f2,f3</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>CreatePain</t>
+  </si>
+  <si>
+    <t>e2 Created</t>
+  </si>
+  <si>
+    <t>f2</t>
+  </si>
+  <si>
+    <t>f3</t>
+  </si>
+  <si>
+    <t>HideOther Choice</t>
+  </si>
+  <si>
+    <t>Hided</t>
+  </si>
+  <si>
+    <t>Destroy</t>
+  </si>
+  <si>
+    <t>哲学</t>
+  </si>
+  <si>
+    <t>f12,f13,f8</t>
+  </si>
+  <si>
+    <t>比较文学</t>
+  </si>
+  <si>
+    <t>f14,f15,f9</t>
+  </si>
+  <si>
+    <t>社会学</t>
+  </si>
+  <si>
+    <t>f16,f17,f10</t>
+  </si>
+  <si>
+    <t>c8</t>
+  </si>
+  <si>
+    <t>开始干活</t>
+  </si>
+  <si>
+    <t>c9</t>
+  </si>
+  <si>
+    <t>干活</t>
+  </si>
+  <si>
+    <t>c10</t>
+  </si>
+  <si>
+    <t>干活！！</t>
+  </si>
+  <si>
+    <t>c11</t>
+  </si>
+  <si>
+    <t>去喝一杯吧</t>
+  </si>
+  <si>
+    <t>c12</t>
+  </si>
+  <si>
+    <t>干活！！！</t>
+  </si>
+  <si>
+    <t>不，你意识到你今晚肯定是写不出来了</t>
+  </si>
+  <si>
+    <t>c13</t>
+  </si>
+  <si>
+    <t>我写了多少了？</t>
+  </si>
+  <si>
+    <t>只有一个大纲，内容基本没有。简单来说：你完了</t>
+  </si>
+  <si>
+    <t>c14</t>
+  </si>
+  <si>
+    <t>可是明天就要交稿了</t>
+  </si>
+  <si>
+    <t>好吧，不管怎么样，明天下午三点前交稿。\n那之前你得去一次那个胖子的办公室。</t>
+  </si>
+  <si>
+    <t>c15</t>
+  </si>
+  <si>
+    <t>还有一个上午，我早上能写的出来的。</t>
+  </si>
+  <si>
+    <t>c16</t>
+  </si>
+  <si>
+    <t>喝</t>
+  </si>
+  <si>
+    <t>f23,f23,f24,f25</t>
+  </si>
+  <si>
+    <t>f1</t>
+  </si>
+  <si>
+    <t>EmotionCreatorTest</t>
+  </si>
+  <si>
+    <t>Raw</t>
+  </si>
+  <si>
+    <t>Raw Card Test</t>
+  </si>
+  <si>
+    <t>c1,c2,c3,c4</t>
+  </si>
+  <si>
+    <t>PainTest</t>
+  </si>
+  <si>
+    <t>Emotion</t>
+  </si>
+  <si>
+    <t>Eternal</t>
+  </si>
+  <si>
+    <t>HapinessTest</t>
+  </si>
+  <si>
+    <t>A mirracle</t>
+  </si>
+  <si>
+    <t>你的文凭</t>
+  </si>
+  <si>
+    <t>你的大学文凭，全世界最没用的东西\n你学的是什么？</t>
+  </si>
+  <si>
+    <t>c5,c6,c7</t>
+  </si>
+  <si>
+    <t>f7</t>
+  </si>
+  <si>
+    <t>你的工作</t>
+  </si>
+  <si>
+    <t>一份勉强能糊口的编剧工作，为一部庸俗短片攥写剧本。明天下午就要交稿了，你还剩最后半天。</t>
+  </si>
+  <si>
+    <t>哲学学位</t>
+  </si>
+  <si>
+    <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。\n\n显然这对找到一份工作没有什么帮助。</t>
+  </si>
+  <si>
+    <t>f9</t>
+  </si>
+  <si>
+    <t>比较文学学位</t>
+  </si>
+  <si>
+    <t>你花了四年时间研究俄罗斯文学，你能熟练解释东正教传统和未来主义在白银时代的演变。\n\n显然这对找到一份工作没有什么帮助。</t>
+  </si>
+  <si>
+    <t>社会学学位</t>
+  </si>
+  <si>
+    <t>你花了四年时间研究黎巴嫩的近代历史，你能熟练叙述宗教冲突如何塑造这个国家里不同阶级的身份认同。\n\n显然这对找到一份工作没有什么帮助。</t>
+  </si>
+  <si>
+    <t>烦躁</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Universal</t>
+  </si>
+  <si>
+    <t>？！？</t>
+  </si>
+  <si>
+    <t>沙漠</t>
+  </si>
+  <si>
     <t>Nature</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战争</t>
   </si>
   <si>
     <t>Politics</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f12,f13,f8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f14,f15,f9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f16,f17,f10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>岛</t>
-  </si>
-  <si>
-    <t>n4</t>
-  </si>
-  <si>
-    <t>n5</t>
-  </si>
-  <si>
-    <t>n6</t>
-  </si>
-  <si>
-    <t>n7</t>
-  </si>
-  <si>
-    <t>平原</t>
-  </si>
-  <si>
-    <t>海</t>
-  </si>
-  <si>
-    <t>高原</t>
-  </si>
-  <si>
-    <t>山</t>
-  </si>
-  <si>
-    <t>大陆</t>
-  </si>
-  <si>
-    <t>荒原</t>
-  </si>
-  <si>
-    <t>丛林</t>
-  </si>
-  <si>
-    <t>城市</t>
-  </si>
-  <si>
-    <t>n8</t>
-  </si>
-  <si>
-    <t>n9</t>
-  </si>
-  <si>
-    <t>n10</t>
-  </si>
-  <si>
-    <t>n11</t>
-  </si>
-  <si>
-    <t>n12</t>
-  </si>
-  <si>
-    <t>n13</t>
-  </si>
-  <si>
-    <t>n14</t>
-  </si>
-  <si>
-    <t>n15</t>
-  </si>
-  <si>
-    <t>n16</t>
-  </si>
-  <si>
-    <t>n17</t>
-  </si>
-  <si>
-    <t>n18</t>
-  </si>
-  <si>
-    <t>n19</t>
-  </si>
-  <si>
-    <t>n20</t>
-  </si>
-  <si>
-    <t>n21</t>
-  </si>
-  <si>
-    <t>n22</t>
-  </si>
-  <si>
-    <t>n23</t>
-  </si>
-  <si>
-    <t>n24</t>
-  </si>
-  <si>
-    <t>n25</t>
-  </si>
-  <si>
-    <t>n26</t>
-  </si>
-  <si>
-    <t>n27</t>
-  </si>
-  <si>
-    <t>f18</t>
-  </si>
-  <si>
-    <t>f19</t>
-  </si>
-  <si>
-    <t>f20</t>
-  </si>
-  <si>
-    <t>f21</t>
-  </si>
-  <si>
-    <t>f22</t>
-  </si>
-  <si>
-    <t>f23</t>
-  </si>
-  <si>
-    <t>f24</t>
-  </si>
-  <si>
-    <t>f25</t>
-  </si>
-  <si>
-    <t>f26</t>
-  </si>
-  <si>
-    <t>f27</t>
-  </si>
-  <si>
-    <t>f28</t>
-  </si>
-  <si>
-    <t>f29</t>
-  </si>
-  <si>
-    <t>f30</t>
-  </si>
-  <si>
-    <t>f31</t>
-  </si>
-  <si>
-    <t>f32</t>
-  </si>
-  <si>
-    <t>f33</t>
-  </si>
-  <si>
-    <t>f34</t>
-  </si>
-  <si>
-    <t>f35</t>
-  </si>
-  <si>
-    <t>f36</t>
+  </si>
+  <si>
+    <t>冻土</t>
+  </si>
+  <si>
+    <t>那些冰冷而坚硬的泥土总是让你想到冻得太过的冰激凌。</t>
+  </si>
+  <si>
+    <t>10岁的时候你找到了妈妈藏在衣柜里的1万块钱。100张颜色鲜艳的纸片，每次想吃麦当劳了你就会偷偷去拿出来几张。\n一个暑假过去，你也不知道你到底偷拿了多少张。不过你清晰地记得妈妈发现时看着你的眼神。</t>
+  </si>
+  <si>
+    <t>你的工作!</t>
+  </si>
+  <si>
+    <t>你写不出来</t>
+  </si>
+  <si>
+    <t>你的工作!!</t>
+  </si>
+  <si>
+    <t>你写不出来，缪斯今晚显然并不眷顾你。\n\n可能也不止今晚。</t>
+  </si>
+  <si>
+    <t>你的工作!!!</t>
+  </si>
+  <si>
+    <t>c11,c12</t>
+  </si>
+  <si>
+    <t>是的，你写不出来了，你不得不承认这个事实。</t>
+  </si>
+  <si>
+    <t>c13,c14,c15</t>
+  </si>
+  <si>
+    <t>酒</t>
+  </si>
+  <si>
+    <t>遗忘</t>
+  </si>
+  <si>
+    <t>世界上唯一的万能药</t>
+  </si>
+  <si>
+    <t>痛苦</t>
+  </si>
+  <si>
+    <t>我们必须想象西西弗斯是幸福的</t>
+  </si>
+  <si>
+    <t>幸福</t>
+  </si>
+  <si>
+    <t>或许在不久的将来你会意识到这不过是一种幻觉，但至少此刻它还不是。它正坚实地躺在你的胃的下方，像个安睡的孩子。</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>NodeName</t>
   </si>
 </sst>
 </file>
@@ -769,7 +858,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -805,6 +894,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1120,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC2FDD69-928B-4F19-A695-2238DDC39BD8}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1132,7 +1227,7 @@
     <col min="8" max="8" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -1149,351 +1244,590 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3">
+      <c r="I1" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="I2" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" s="12">
         <v>-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4">
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="12">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" t="b">
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" t="b">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="I6" s="12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" t="b">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" t="b">
+      <c r="H7" s="12"/>
+      <c r="I7" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10">
+      <c r="H8" s="12"/>
+      <c r="I8" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12">
         <v>-1</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="I17" s="12"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="12"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I19" s="12"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="I20" s="12"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B21" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="I21" s="12"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="E22" s="12">
+        <v>3</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="E11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="B23" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" s="12">
+        <v>-2</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="C12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="B24" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E24" s="12">
+        <v>5</v>
+      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>115</v>
       </c>
-      <c r="C13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" t="s">
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>174</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1504,7 +1838,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB045CFD-59DE-4DB8-AAE0-76824A362221}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1514,9 +1848,12 @@
     <col min="5" max="5" width="14.875" customWidth="1"/>
     <col min="6" max="6" width="17.625" customWidth="1"/>
     <col min="7" max="7" width="23.125" customWidth="1"/>
+    <col min="8" max="8" width="16.125" customWidth="1"/>
+    <col min="9" max="9" width="15.5" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -1538,130 +1875,356 @@
       <c r="G1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="H1" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="F3" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" t="b">
+      <c r="B8" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="G2" t="b">
+      <c r="G13" s="12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" t="b">
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="G3" t="b">
+      <c r="G14" s="12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="b">
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="b">
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="I17" s="13">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1677,119 +2240,119 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M1" t="s">
-        <v>79</v>
-      </c>
       <c r="N1" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="O1" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="P1" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="Q1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="R1" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -1810,10 +2373,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -1834,10 +2397,10 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -1858,10 +2421,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -1882,10 +2445,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1906,10 +2469,10 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1930,10 +2493,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1954,10 +2517,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -1978,10 +2541,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -2002,10 +2565,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -2026,10 +2589,10 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -2050,10 +2613,10 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -2074,10 +2637,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -2098,10 +2661,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -2122,10 +2685,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -2146,10 +2709,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -2182,297 +2745,297 @@
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="2" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="D1" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="E1" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="F1" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="G1" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="H1" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="I1" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="J1" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="K1" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="L1" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="M1" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>132</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2488,21 +3051,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E1" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -2510,17 +3073,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2536,21 +3099,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E1" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -2558,17 +3121,36 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A688C2E-2507-43A9-9C2A-41277BDD4C05}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C007FD0-10F3-4544-B2F4-348F07855E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1D605B-897F-4E47-96EA-47A82396A0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="257">
   <si>
     <t>Index</t>
   </si>
@@ -670,9 +670,6 @@
     <t>Museum</t>
   </si>
   <si>
-    <t>Node_small</t>
-  </si>
-  <si>
     <t>OverGround</t>
   </si>
   <si>
@@ -689,23 +686,6 @@
   </si>
   <si>
     <t>Supermarket</t>
-  </si>
-  <si>
-    <t>Underground</t>
-  </si>
-  <si>
-    <t>Underground (1)</t>
-  </si>
-  <si>
-    <t>Underground (2)</t>
-  </si>
-  <si>
-    <t>m1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>m2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>m3</t>
@@ -803,6 +783,21 @@
   <si>
     <t>或许在不久的将来你会意识到这不过是一种幻觉，但至少此刻它还不是，现在它正坚实地躺在你的胃的下方，像个安睡的孩子。 \n 消耗：意志力+5</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>m2</t>
+  </si>
+  <si>
+    <t>Yourbed</t>
+  </si>
+  <si>
+    <t>Underground_Home</t>
+  </si>
+  <si>
+    <t>Underground_Downtown</t>
+  </si>
+  <si>
+    <t>Underground_Book</t>
   </si>
 </sst>
 </file>
@@ -848,13 +843,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
       <family val="3"/>
@@ -882,8 +870,16 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -920,6 +916,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF258"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1002,7 +1004,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1011,13 +1013,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1274,564 +1276,564 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" s="12" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="12" t="b">
+      <c r="I2" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>-2</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12" t="b">
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>2</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12" t="b">
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="12" t="s">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="12" t="b">
+      <c r="I5" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="13" t="s">
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I6" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11">
+        <v>-1</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E22" s="11">
+        <v>3</v>
+      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" s="11">
+        <v>-2</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E24" s="11">
+        <v>5</v>
+      </c>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="I6" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12">
-        <v>-1</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="I18" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="I20" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I21" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="E22" s="12">
-        <v>3</v>
-      </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E23" s="12">
-        <v>-2</v>
-      </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="E24" s="12">
-        <v>5</v>
-      </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="I25" s="12" t="b">
+      <c r="I25" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1860,555 +1862,555 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="14" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="b">
+      <c r="E2" s="11"/>
+      <c r="F2" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="G2" s="12" t="b">
+      <c r="G2" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="12" t="b">
+      <c r="F3" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="G3" s="12" t="b">
+      <c r="G3" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="12" t="b">
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12" t="b">
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="G5" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="11"/>
+      <c r="D6" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="11"/>
+      <c r="D7" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12" t="s">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13" t="s">
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
+      <c r="F9" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
+      <c r="F10" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13" t="s">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
+      <c r="F11" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13" t="s">
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
+      <c r="F12" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="12" t="b">
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="G13" s="12" t="b">
+      <c r="G13" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="12" t="b">
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="G14" s="12" t="b">
+      <c r="G14" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12" t="s">
-        <v>252</v>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="12" t="b">
+      <c r="B15" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12" t="s">
-        <v>252</v>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="12" t="b">
+      <c r="C16" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" s="13" t="s">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="12">
         <v>2</v>
       </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="A18" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -3332,179 +3334,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="16" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="B2" t="s">
-        <v>203</v>
+        <v>246</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B3" t="s">
-        <v>204</v>
+        <v>252</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" t="s">
-        <v>205</v>
+        <v>220</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" t="s">
-        <v>206</v>
+        <v>221</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" t="s">
-        <v>207</v>
+        <v>222</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" t="s">
-        <v>208</v>
+        <v>223</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B8" t="s">
-        <v>209</v>
+        <v>224</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="B9" t="s">
-        <v>210</v>
+        <v>225</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B10" t="s">
-        <v>211</v>
+        <v>226</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B11" t="s">
-        <v>212</v>
+        <v>227</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B12" t="s">
-        <v>213</v>
+        <v>228</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="B13" t="s">
-        <v>214</v>
+        <v>229</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="B14" t="s">
-        <v>215</v>
+        <v>230</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B15" t="s">
-        <v>216</v>
+        <v>231</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B16" t="s">
-        <v>217</v>
+        <v>232</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B17" t="s">
-        <v>218</v>
+        <v>233</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B18" t="s">
-        <v>219</v>
+        <v>234</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B19" t="s">
-        <v>220</v>
+        <v>235</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B20" t="s">
-        <v>221</v>
+        <v>236</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B21" t="s">
-        <v>222</v>
+        <v>237</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="B22" t="s">
-        <v>223</v>
+        <v>238</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1D605B-897F-4E47-96EA-47A82396A0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3887D670-6387-4D9E-93C5-E8CCBA628CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="277">
   <si>
     <t>Index</t>
   </si>
@@ -121,18 +121,12 @@
     <t>哲学学位</t>
   </si>
   <si>
-    <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。\n\n显然这对找到一份工作没有什么帮助。</t>
-  </si>
-  <si>
     <t>f9</t>
   </si>
   <si>
     <t>比较文学学位</t>
   </si>
   <si>
-    <t>你花了四年时间研究俄罗斯文学，你能熟练解释东正教传统和未来主义在白银时代的演变。\n\n显然这对找到一份工作没有什么帮助。</t>
-  </si>
-  <si>
     <t>f10</t>
   </si>
   <si>
@@ -223,9 +217,6 @@
     <t>你的工作!!</t>
   </si>
   <si>
-    <t>你写不出来，缪斯今晚显然并不眷顾你。\n\n可能也不止今晚。</t>
-  </si>
-  <si>
     <t>c10</t>
   </si>
   <si>
@@ -748,9 +739,6 @@
     <t>c8,c13</t>
   </si>
   <si>
-    <t>正题：你能用它来解决任何问题。\n 反题：解决完之后那些问题会变得没用。\n 合题：但是你能用它来解决任何问题</t>
-  </si>
-  <si>
     <t>世界上唯一的万能药 \n 消耗：意志力+3</t>
   </si>
   <si>
@@ -781,23 +769,103 @@
     <t>压缩</t>
   </si>
   <si>
-    <t>或许在不久的将来你会意识到这不过是一种幻觉，但至少此刻它还不是，现在它正坚实地躺在你的胃的下方，像个安睡的孩子。 \n 消耗：意志力+5</t>
+    <t>m2</t>
+  </si>
+  <si>
+    <t>Yourbed</t>
+  </si>
+  <si>
+    <t>Underground_Home</t>
+  </si>
+  <si>
+    <t>Underground_Downtown</t>
+  </si>
+  <si>
+    <t>Underground_Book</t>
+  </si>
+  <si>
+    <t>\n\n每天不能喝太多。</t>
+  </si>
+  <si>
+    <t>或许在不久的将来你会意识到这不过是一种幻觉，但至少此刻它还不是。它正坚实地躺在你的胃的下方，像个安睡的孩子。 \n 消耗：意志力+5</t>
+  </si>
+  <si>
+    <t>f27</t>
+  </si>
+  <si>
+    <t>烟</t>
+  </si>
+  <si>
+    <t>可以让你清醒一点，但对身体不太好。\n\n每天不能抽太多。</t>
+  </si>
+  <si>
+    <t>c18</t>
+  </si>
+  <si>
+    <t>f28</t>
+  </si>
+  <si>
+    <t>维他柠檬茶</t>
+  </si>
+  <si>
+    <t>上学的时候，你最幸福的事情就是翻墙到学校后面的超市买柠檬茶喝。\n\n对于成年人来说有些太甜了。</t>
+  </si>
+  <si>
+    <t>c19</t>
+  </si>
+  <si>
+    <t>f29</t>
+  </si>
+  <si>
+    <t>f30</t>
+  </si>
+  <si>
+    <t>灰</t>
+  </si>
+  <si>
+    <t>f31</t>
+  </si>
+  <si>
+    <t>f32</t>
+  </si>
+  <si>
+    <t>f33</t>
+  </si>
+  <si>
+    <t>f34</t>
+  </si>
+  <si>
+    <t>f35</t>
+  </si>
+  <si>
+    <t>f36</t>
+  </si>
+  <si>
+    <t>抽烟</t>
+  </si>
+  <si>
+    <t>f29,f30</t>
+  </si>
+  <si>
+    <t>正题：你能用它来解决任何问题。 
+反题：解决完之后那些问题会变得没用。
+合题：但是你能用它来解决任何问题</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>m2</t>
-  </si>
-  <si>
-    <t>Yourbed</t>
-  </si>
-  <si>
-    <t>Underground_Home</t>
-  </si>
-  <si>
-    <t>Underground_Downtown</t>
-  </si>
-  <si>
-    <t>Underground_Book</t>
+    <t>你写不出来，缪斯今晚显然并不眷顾你。
+可能也不止今晚。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>你花了四年时间研究俄罗斯文学，你能熟练解释东正教传统和未来主义在白银时代的演变。
+显然这对找到一份工作没有什么帮助。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。
+显然这对找到一份工作没有什么帮助。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -970,7 +1038,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1021,6 +1089,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1234,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1247,31 +1324,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1390,13 +1467,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I6" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1406,8 +1483,8 @@
       <c r="C7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>31</v>
+      <c r="D7" s="19" t="s">
+        <v>276</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -1419,18 +1496,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>32</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>33</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>34</v>
+      <c r="D8" s="19" t="s">
+        <v>275</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -1444,16 +1521,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -1467,15 +1544,15 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D10" s="17"/>
       <c r="E10" s="11">
         <v>-1</v>
       </c>
@@ -1486,22 +1563,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>240</v>
+      <c r="D11" s="18" t="s">
+        <v>273</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
@@ -1511,20 +1588,20 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>46</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
@@ -1534,18 +1611,18 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="12"/>
       <c r="F13" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
@@ -1555,18 +1632,18 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="12"/>
       <c r="F14" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
@@ -1576,20 +1653,20 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>55</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
@@ -1599,20 +1676,20 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>58</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
@@ -1622,16 +1699,16 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
@@ -1639,24 +1716,24 @@
         <v>1</v>
       </c>
       <c r="H17" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="I17" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>64</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>65</v>
+      <c r="D18" s="19" t="s">
+        <v>274</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
@@ -1664,24 +1741,24 @@
         <v>1</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I18" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
@@ -1689,15 +1766,15 @@
         <v>1</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I19" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>26</v>
@@ -1706,7 +1783,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
@@ -1714,47 +1791,49 @@
         <v>1</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I20" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="13" t="s">
+        <v>252</v>
+      </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I21" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E22" s="11">
         <v>3</v>
@@ -1763,21 +1842,21 @@
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E23" s="11">
         <v>-2</v>
@@ -1786,21 +1865,21 @@
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E24" s="11">
         <v>5</v>
@@ -1809,21 +1888,21 @@
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="11"/>
@@ -1831,21 +1910,194 @@
         <v>1</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I25" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="I26" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="I27" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11" t="b">
         <v>0</v>
       </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1866,48 +2118,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>91</v>
-      </c>
       <c r="K1" s="14" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>95</v>
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11" t="b">
@@ -1923,13 +2175,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>14</v>
@@ -1950,13 +2202,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -1973,10 +2225,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
@@ -1994,14 +2246,14 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11" t="b">
@@ -2017,14 +2269,14 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11" t="b">
@@ -2040,14 +2292,14 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11" t="b">
@@ -2066,12 +2318,12 @@
         <v>28</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
       <c r="E9" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F9" s="11" t="b">
         <v>1</v>
@@ -2086,15 +2338,15 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
       <c r="E10" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F10" s="11" t="b">
         <v>1</v>
@@ -2109,15 +2361,15 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
       <c r="E11" s="12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F11" s="11" t="b">
         <v>1</v>
@@ -2132,15 +2384,15 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F12" s="11" t="b">
         <v>1</v>
@@ -2155,13 +2407,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
@@ -2178,13 +2430,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
@@ -2198,18 +2450,18 @@
       <c r="I14" s="12"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
@@ -2223,18 +2475,18 @@
       <c r="I15" s="12"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
@@ -2249,12 +2501,12 @@
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2266,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I17" s="12">
         <v>2</v>
@@ -2274,12 +2526,12 @@
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2295,33 +2547,71 @@
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>271</v>
+      </c>
       <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
+      <c r="D19" s="11" t="s">
+        <v>272</v>
+      </c>
       <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="F19" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="15"/>
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>124</v>
+      </c>
       <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
+      <c r="D20" s="11" t="s">
+        <v>77</v>
+      </c>
       <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="F20" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="11" t="b">
+        <v>1</v>
+      </c>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="11"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -2334,7 +2624,7 @@
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="11"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -2347,7 +2637,7 @@
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -2360,7 +2650,7 @@
       <c r="J23" s="12"/>
       <c r="K23" s="12"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="11"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -2373,7 +2663,7 @@
       <c r="J24" s="12"/>
       <c r="K24" s="12"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="11"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -2386,7 +2676,7 @@
       <c r="J25" s="12"/>
       <c r="K25" s="12"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -2399,7 +2689,7 @@
       <c r="J26" s="12"/>
       <c r="K26" s="12"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="11"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -2425,119 +2715,119 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" t="s">
         <v>129</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>130</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>131</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>132</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>133</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>134</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>135</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>136</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>137</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>138</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>139</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>140</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>141</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>142</v>
-      </c>
-      <c r="P1" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>144</v>
-      </c>
-      <c r="R1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="M2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="Q2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="8" t="s">
         <v>155</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -2558,10 +2848,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -2582,10 +2872,10 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -2606,10 +2896,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -2630,10 +2920,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -2654,10 +2944,10 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -2678,10 +2968,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -2702,10 +2992,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -2726,10 +3016,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -2750,10 +3040,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -2774,10 +3064,10 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -2798,10 +3088,10 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -2822,10 +3112,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -2846,10 +3136,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -2870,10 +3160,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -2894,10 +3184,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -2930,297 +3220,297 @@
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" t="s">
         <v>159</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>160</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>161</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>162</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>163</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>164</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>165</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>166</v>
-      </c>
-      <c r="K1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L1" t="s">
-        <v>168</v>
-      </c>
-      <c r="M1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E2" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3236,21 +3526,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3258,17 +3548,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -3284,21 +3574,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3306,17 +3596,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3338,175 +3628,175 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3887D670-6387-4D9E-93C5-E8CCBA628CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456DD0BD-9009-4DAE-8A9D-EDC50588633C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,18 @@
     <sheet name="ForgeLibrary_Emotion" sheetId="7" r:id="rId6"/>
     <sheet name="Node" sheetId="10" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -52,9 +63,6 @@
     <t>Choices</t>
   </si>
   <si>
-    <t>CanBeDropped</t>
-  </si>
-  <si>
     <t>f1</t>
   </si>
   <si>
@@ -865,6 +873,10 @@
   <si>
     <t>你花了四年时间研究德国观念论，你能熟练使用范畴，感性确定性，统觉等一堆不知所云的概念解释人为什么能看到颜色。
 显然这对找到一份工作没有什么帮助。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanBeDropped</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -883,24 +895,28 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1349,21 +1365,21 @@
         <v>7</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>8</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>12</v>
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
@@ -1371,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I2" s="11" t="b">
         <v>1</v>
@@ -1379,16 +1395,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="C3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>16</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="E3" s="11">
         <v>-2</v>
@@ -1397,21 +1413,21 @@
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
       <c r="I3" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>20</v>
       </c>
       <c r="E4" s="11">
         <v>2</v>
@@ -1420,21 +1436,21 @@
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>23</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
@@ -1442,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I5" s="11" t="b">
         <v>1</v>
@@ -1450,16 +1466,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>27</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
@@ -1467,24 +1483,24 @@
         <v>1</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I6" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>30</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -1498,16 +1514,16 @@
     </row>
     <row r="8" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>32</v>
-      </c>
       <c r="C8" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -1521,16 +1537,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>34</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>35</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -1544,13 +1560,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>37</v>
-      </c>
       <c r="C10" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="11">
@@ -1560,25 +1576,25 @@
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="C11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>40</v>
-      </c>
       <c r="D11" s="18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
@@ -1588,20 +1604,20 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="C12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>44</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
@@ -1611,18 +1627,18 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>46</v>
-      </c>
       <c r="C13" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="12"/>
       <c r="F13" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
@@ -1632,18 +1648,18 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>49</v>
-      </c>
       <c r="C14" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="12"/>
       <c r="F14" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
@@ -1653,20 +1669,20 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="C15" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>52</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>53</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
@@ -1676,20 +1692,20 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="C16" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>56</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
@@ -1699,16 +1715,16 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="C17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
@@ -1716,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I17" s="11" t="b">
         <v>1</v>
@@ -1724,16 +1740,16 @@
     </row>
     <row r="18" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>62</v>
-      </c>
       <c r="C18" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
@@ -1741,7 +1757,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I18" s="11" t="b">
         <v>1</v>
@@ -1749,16 +1765,16 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="C19" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
@@ -1766,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I19" s="11" t="b">
         <v>1</v>
@@ -1774,16 +1790,16 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>67</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>68</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
@@ -1791,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I20" s="11" t="b">
         <v>1</v>
@@ -1799,16 +1815,16 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="C21" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
@@ -1816,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I21" s="11" t="b">
         <v>1</v>
@@ -1824,16 +1840,16 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>74</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E22" s="11">
         <v>3</v>
@@ -1847,16 +1863,16 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>76</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E23" s="11">
         <v>-2</v>
@@ -1870,16 +1886,16 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>78</v>
-      </c>
       <c r="C24" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E24" s="11">
         <v>5</v>
@@ -1893,16 +1909,16 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B25" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>239</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>240</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="11"/>
@@ -1910,7 +1926,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I25" s="11" t="b">
         <v>1</v>
@@ -1918,16 +1934,16 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="C26" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>255</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>256</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
@@ -1935,7 +1951,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I26" s="11" t="b">
         <v>1</v>
@@ -1943,16 +1959,16 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="C27" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="13" t="s">
         <v>259</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>260</v>
       </c>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
@@ -1960,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I27" s="11" t="b">
         <v>1</v>
@@ -1968,18 +1984,18 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
@@ -1989,18 +2005,18 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>264</v>
-      </c>
       <c r="C29" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
@@ -2010,7 +2026,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -2020,12 +2036,12 @@
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -2038,7 +2054,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -2051,7 +2067,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -2064,7 +2080,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -2077,7 +2093,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -2118,48 +2134,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="J1" s="14" t="s">
-        <v>88</v>
-      </c>
       <c r="K1" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>91</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>92</v>
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11" t="b">
@@ -2175,19 +2191,19 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="C3" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="D3" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" s="11" t="b">
         <v>0</v>
@@ -2202,13 +2218,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>98</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -2225,10 +2241,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>100</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
@@ -2246,14 +2262,14 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>102</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11" t="b">
@@ -2269,14 +2285,14 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>104</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>105</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11" t="b">
@@ -2292,14 +2308,14 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>108</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11" t="b">
@@ -2315,15 +2331,15 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
       <c r="E9" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="11" t="b">
         <v>1</v>
@@ -2338,15 +2354,15 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
       <c r="E10" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F10" s="11" t="b">
         <v>1</v>
@@ -2361,15 +2377,15 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
       <c r="E11" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" s="11" t="b">
         <v>1</v>
@@ -2384,15 +2400,15 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>114</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F12" s="11" t="b">
         <v>1</v>
@@ -2407,13 +2423,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="C13" s="12" t="s">
         <v>116</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>117</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
@@ -2430,13 +2446,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="C14" s="12" t="s">
         <v>119</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>120</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
@@ -2450,18 +2466,18 @@
       <c r="I14" s="12"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>243</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>244</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
@@ -2475,18 +2491,18 @@
       <c r="I15" s="12"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>123</v>
-      </c>
       <c r="C16" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
@@ -2503,10 +2519,10 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2518,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I17" s="12">
         <v>2</v>
@@ -2528,10 +2544,10 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2549,14 +2565,14 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="11" t="b">
@@ -2581,14 +2597,14 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="11" t="b">
@@ -2715,119 +2731,119 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" t="s">
         <v>126</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>127</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>128</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>129</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>130</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>131</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>132</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>133</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>134</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>135</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>136</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>137</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>138</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>139</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>140</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>141</v>
-      </c>
-      <c r="R1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="Q2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" s="8" t="s">
         <v>154</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -2848,10 +2864,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -2872,10 +2888,10 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -2896,10 +2912,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -2920,10 +2936,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -2944,10 +2960,10 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -2968,10 +2984,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -2992,10 +3008,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -3016,10 +3032,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -3040,10 +3056,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -3064,10 +3080,10 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -3088,10 +3104,10 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -3112,10 +3128,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -3136,10 +3152,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -3160,10 +3176,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -3184,10 +3200,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -3220,297 +3236,297 @@
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" t="s">
         <v>156</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>157</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>158</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>159</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>160</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>161</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>162</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>163</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>164</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>165</v>
-      </c>
-      <c r="M1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -3526,21 +3542,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1" t="s">
         <v>192</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>193</v>
-      </c>
-      <c r="E1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3548,17 +3564,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3574,21 +3590,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" t="s">
         <v>195</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>196</v>
-      </c>
-      <c r="E1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3596,17 +3612,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -3628,175 +3644,175 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456DD0BD-9009-4DAE-8A9D-EDC50588633C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CDCCA2-A7F4-4CE1-90F3-F61436CAF648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
@@ -2337,8 +2337,7 @@
         <v>109</v>
       </c>
       <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>56</v>
       </c>
       <c r="F9" s="11" t="b">
@@ -2360,8 +2359,7 @@
         <v>110</v>
       </c>
       <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12" t="s">
+      <c r="D10" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F10" s="11" t="b">
@@ -2383,8 +2381,7 @@
         <v>111</v>
       </c>
       <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12" t="s">
+      <c r="D11" s="12" t="s">
         <v>63</v>
       </c>
       <c r="F11" s="11" t="b">
@@ -2406,8 +2403,7 @@
         <v>113</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12" t="s">
+      <c r="D12" s="12" t="s">
         <v>66</v>
       </c>
       <c r="F12" s="11" t="b">

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CDCCA2-A7F4-4CE1-90F3-F61436CAF648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52898FDA-E967-461D-96BB-483F57446612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52898FDA-E967-461D-96BB-483F57446612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC31100-64CC-465D-B948-F97276DC53EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="ForgeLibrary_Politics" sheetId="9" r:id="rId5"/>
     <sheet name="ForgeLibrary_Emotion" sheetId="7" r:id="rId6"/>
     <sheet name="Node" sheetId="10" r:id="rId7"/>
+    <sheet name="DailyMission" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="284">
   <si>
     <t>Index</t>
   </si>
@@ -877,6 +878,34 @@
   </si>
   <si>
     <t>CanBeDropped</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Index</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>dm1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoneyReward</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequiredCards</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A Vampire Story</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f29,f30</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -884,7 +913,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -956,6 +985,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -1054,7 +1090,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1114,6 +1150,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3815,4 +3854,51 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAF9A1A-285A-4BA7-8832-B2D0F52F1F9B}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="20"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC31100-64CC-465D-B948-F97276DC53EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3A6BCA-8F34-4596-8283-D4CCD6B4876A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="239">
   <si>
     <t>Index</t>
   </si>
@@ -346,9 +346,6 @@
     <t>哲学</t>
   </si>
   <si>
-    <t>f12,f13,f8</t>
-  </si>
-  <si>
     <t>c6</t>
   </si>
   <si>
@@ -418,201 +415,9 @@
     <t>Forge_Index</t>
   </si>
   <si>
-    <t>u1</t>
-  </si>
-  <si>
-    <t>u2</t>
-  </si>
-  <si>
-    <t>u3</t>
-  </si>
-  <si>
-    <t>u4</t>
-  </si>
-  <si>
-    <t>u5</t>
-  </si>
-  <si>
-    <t>u6</t>
-  </si>
-  <si>
-    <t>u7</t>
-  </si>
-  <si>
-    <t>u8</t>
-  </si>
-  <si>
-    <t>u9</t>
-  </si>
-  <si>
-    <t>u10</t>
-  </si>
-  <si>
-    <t>u11</t>
-  </si>
-  <si>
-    <t>u12</t>
-  </si>
-  <si>
-    <t>u13</t>
-  </si>
-  <si>
-    <t>u14</t>
-  </si>
-  <si>
-    <t>u15</t>
-  </si>
-  <si>
-    <t>u16</t>
-  </si>
-  <si>
-    <t>火</t>
-  </si>
-  <si>
-    <t>冬</t>
-  </si>
-  <si>
-    <t>铁</t>
-  </si>
-  <si>
-    <t>空气</t>
-  </si>
-  <si>
-    <t>世界</t>
-  </si>
-  <si>
-    <t>大地</t>
-  </si>
-  <si>
-    <t>熵</t>
-  </si>
-  <si>
-    <t>死亡</t>
-  </si>
-  <si>
     <t>理性</t>
   </si>
   <si>
-    <t>帝国</t>
-  </si>
-  <si>
-    <t>奇迹</t>
-  </si>
-  <si>
-    <t>爱</t>
-  </si>
-  <si>
-    <t>零</t>
-  </si>
-  <si>
-    <t>n1</t>
-  </si>
-  <si>
-    <t>n2</t>
-  </si>
-  <si>
-    <t>n3</t>
-  </si>
-  <si>
-    <t>n4</t>
-  </si>
-  <si>
-    <t>n5</t>
-  </si>
-  <si>
-    <t>n6</t>
-  </si>
-  <si>
-    <t>n7</t>
-  </si>
-  <si>
-    <t>n8</t>
-  </si>
-  <si>
-    <t>n9</t>
-  </si>
-  <si>
-    <t>n10</t>
-  </si>
-  <si>
-    <t>n11</t>
-  </si>
-  <si>
-    <t>平原</t>
-  </si>
-  <si>
-    <t>海</t>
-  </si>
-  <si>
-    <t>高原</t>
-  </si>
-  <si>
-    <t>山</t>
-  </si>
-  <si>
-    <t>岛</t>
-  </si>
-  <si>
-    <t>大陆</t>
-  </si>
-  <si>
-    <t>荒原</t>
-  </si>
-  <si>
-    <t>丛林</t>
-  </si>
-  <si>
-    <t>城市</t>
-  </si>
-  <si>
-    <t>n12</t>
-  </si>
-  <si>
-    <t>n13</t>
-  </si>
-  <si>
-    <t>n14</t>
-  </si>
-  <si>
-    <t>n15</t>
-  </si>
-  <si>
-    <t>n16</t>
-  </si>
-  <si>
-    <t>n17</t>
-  </si>
-  <si>
-    <t>n18</t>
-  </si>
-  <si>
-    <t>n19</t>
-  </si>
-  <si>
-    <t>n20</t>
-  </si>
-  <si>
-    <t>n21</t>
-  </si>
-  <si>
-    <t>n22</t>
-  </si>
-  <si>
-    <t>n23</t>
-  </si>
-  <si>
-    <t>n24</t>
-  </si>
-  <si>
-    <t>n25</t>
-  </si>
-  <si>
-    <t>n26</t>
-  </si>
-  <si>
-    <t>n27</t>
-  </si>
-  <si>
     <t>p1</t>
   </si>
   <si>
@@ -823,9 +628,6 @@
     <t>c19</t>
   </si>
   <si>
-    <t>f29</t>
-  </si>
-  <si>
     <t>f30</t>
   </si>
   <si>
@@ -833,21 +635,6 @@
   </si>
   <si>
     <t>f31</t>
-  </si>
-  <si>
-    <t>f32</t>
-  </si>
-  <si>
-    <t>f33</t>
-  </si>
-  <si>
-    <t>f34</t>
-  </si>
-  <si>
-    <t>f35</t>
-  </si>
-  <si>
-    <t>f36</t>
   </si>
   <si>
     <t>抽烟</t>
@@ -901,11 +688,111 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>A Vampire Story</t>
+    <t>f29,f30</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>f29,f30</t>
+    <t>f29</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f29</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f12</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f13</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f30</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>test</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Raw</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>c20</t>
+  </si>
+  <si>
+    <t>c20</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>testCard</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>辩证法</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f12,f13,f29,f30,f31</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>谜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>理性</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>灰</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>痛苦</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f12,f13,f8,f31</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>dm2</t>
+  </si>
+  <si>
+    <t>dm3</t>
+  </si>
+  <si>
+    <t>dm4</t>
+  </si>
+  <si>
+    <t>理性灰</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冻土沙漠</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>辩证法理性</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>理性沙漠</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f14,f16</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f29,f14</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f29,f12</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1090,7 +977,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1152,6 +1039,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1404,7 +1297,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>276</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -1522,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="I6" s="11" t="b">
         <v>1</v>
@@ -1539,7 +1432,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -1562,7 +1455,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>274</v>
+        <v>203</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -1629,7 +1522,7 @@
         <v>39</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>272</v>
+        <v>201</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="11" t="s">
@@ -1788,7 +1681,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>273</v>
+        <v>202</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
@@ -1863,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>251</v>
+        <v>186</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
@@ -1888,7 +1781,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="E22" s="11">
         <v>3</v>
@@ -1911,7 +1804,7 @@
         <v>15</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="E23" s="11">
         <v>-2</v>
@@ -1934,7 +1827,7 @@
         <v>15</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>252</v>
+        <v>187</v>
       </c>
       <c r="E24" s="11">
         <v>5</v>
@@ -1951,13 +1844,13 @@
         <v>78</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="11"/>
@@ -1965,7 +1858,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="I25" s="11" t="b">
         <v>1</v>
@@ -1973,16 +1866,16 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>254</v>
+        <v>189</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>255</v>
+        <v>190</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
@@ -1990,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c r="I26" s="11" t="b">
         <v>1</v>
@@ -1998,16 +1891,16 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>257</v>
+        <v>192</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>258</v>
+        <v>193</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>259</v>
+        <v>194</v>
       </c>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
@@ -2015,18 +1908,18 @@
         <v>1</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="I27" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
-        <v>261</v>
+      <c r="A28" s="21" t="s">
+        <v>212</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>39</v>
@@ -2044,10 +1937,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>262</v>
+        <v>196</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>263</v>
+        <v>197</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>39</v>
@@ -2055,7 +1948,7 @@
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
@@ -2065,24 +1958,31 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
+        <v>198</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>221</v>
+      </c>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
+      <c r="G30" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>220</v>
+      </c>
       <c r="I30" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B31" s="11"/>
+      <c r="A31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
@@ -2092,9 +1992,7 @@
       <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
-        <v>266</v>
-      </c>
+      <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -2105,9 +2003,7 @@
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="11" t="s">
-        <v>267</v>
-      </c>
+      <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
@@ -2118,9 +2014,7 @@
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="11" t="s">
-        <v>268</v>
-      </c>
+      <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
@@ -2131,9 +2025,7 @@
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
-        <v>269</v>
-      </c>
+      <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
@@ -2200,7 +2092,7 @@
         <v>87</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>198</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -2307,8 +2199,8 @@
         <v>101</v>
       </c>
       <c r="C6" s="11"/>
-      <c r="D6" s="11" t="s">
-        <v>102</v>
+      <c r="D6" s="21" t="s">
+        <v>228</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11" t="b">
@@ -2324,14 +2216,14 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11" t="b">
@@ -2347,14 +2239,14 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>106</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>107</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11" t="b">
@@ -2373,7 +2265,7 @@
         <v>27</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="12" t="s">
@@ -2395,7 +2287,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
@@ -2417,7 +2309,7 @@
         <v>62</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
@@ -2436,10 +2328,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>112</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
@@ -2458,13 +2350,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="C13" s="12" t="s">
         <v>115</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>116</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
@@ -2481,13 +2373,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="C14" s="12" t="s">
         <v>118</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>119</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
@@ -2501,18 +2393,18 @@
       <c r="I14" s="12"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
@@ -2526,18 +2418,18 @@
       <c r="I15" s="12"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>122</v>
-      </c>
       <c r="C16" s="12" t="s">
-        <v>244</v>
+        <v>179</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
@@ -2557,7 +2449,7 @@
         <v>71</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2569,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I17" s="12">
         <v>2</v>
@@ -2579,10 +2471,10 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2600,14 +2492,14 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>270</v>
+        <v>199</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="11" t="s">
-        <v>271</v>
+        <v>200</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="11" t="b">
@@ -2632,10 +2524,10 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="11" t="s">
@@ -2663,13 +2555,23 @@
       <c r="T20" s="12"/>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
+      <c r="A21" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>217</v>
+      </c>
       <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
+      <c r="D21" s="22" t="s">
+        <v>223</v>
+      </c>
       <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+      <c r="F21" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="11" t="b">
+        <v>1</v>
+      </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
@@ -2766,124 +2668,72 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J1" t="s">
-        <v>133</v>
-      </c>
-      <c r="K1" t="s">
-        <v>134</v>
-      </c>
-      <c r="L1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M1" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O1" t="s">
-        <v>138</v>
-      </c>
-      <c r="P1" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>140</v>
-      </c>
-      <c r="R1" t="s">
-        <v>141</v>
+        <v>124</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q2" s="7" t="s">
+      <c r="F2" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="8"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="4"/>
+      <c r="C3" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="G3" s="4"/>
       <c r="H3" s="6"/>
       <c r="I3" s="4"/>
@@ -2898,16 +2748,24 @@
       <c r="R3" s="6"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="A4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>227</v>
+      </c>
       <c r="G4" s="5"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -2922,16 +2780,24 @@
       <c r="R4" s="6"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="A5" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -2946,16 +2812,24 @@
       <c r="R5" s="6"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="A6" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>226</v>
+      </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -2970,12 +2844,7 @@
       <c r="R6" s="6"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>146</v>
-      </c>
+      <c r="B7" s="6"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -2994,12 +2863,7 @@
       <c r="R7" s="6"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>147</v>
-      </c>
+      <c r="B8" s="6"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -3018,12 +2882,7 @@
       <c r="R8" s="6"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>148</v>
-      </c>
+      <c r="B9" s="6"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -3042,12 +2901,7 @@
       <c r="R9" s="6"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="B10" s="6"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -3066,12 +2920,7 @@
       <c r="R10" s="6"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>150</v>
-      </c>
+      <c r="B11" s="6"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -3090,12 +2939,7 @@
       <c r="R11" s="6"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>135</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>151</v>
-      </c>
+      <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -3114,12 +2958,7 @@
       <c r="R12" s="4"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="B13" s="6"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -3138,12 +2977,7 @@
       <c r="R13" s="6"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>42</v>
-      </c>
+      <c r="B14" s="6"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -3162,12 +2996,7 @@
       <c r="R14" s="6"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>152</v>
-      </c>
+      <c r="B15" s="6"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -3186,12 +3015,7 @@
       <c r="R15" s="6"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>153</v>
-      </c>
+      <c r="B16" s="6"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -3209,13 +3033,8 @@
       <c r="Q16" s="4"/>
       <c r="R16" s="6"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>38</v>
-      </c>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B17" s="7"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -3233,13 +3052,8 @@
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>141</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>154</v>
-      </c>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B18" s="8"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -3271,298 +3085,100 @@
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J1" t="s">
-        <v>162</v>
-      </c>
-      <c r="K1" t="s">
-        <v>163</v>
-      </c>
-      <c r="L1" t="s">
-        <v>164</v>
-      </c>
-      <c r="M1" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>174</v>
-      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>142</v>
-      </c>
+      <c r="B3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>143</v>
-      </c>
+      <c r="B4" s="6"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>144</v>
-      </c>
+      <c r="B5" s="6"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>145</v>
-      </c>
+      <c r="B6" s="6"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>146</v>
-      </c>
+      <c r="B7" s="6"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>160</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>147</v>
-      </c>
+      <c r="B8" s="6"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>148</v>
-      </c>
+      <c r="B9" s="6"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>162</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="B10" s="6"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>150</v>
-      </c>
+      <c r="B11" s="6"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>151</v>
-      </c>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="B13" s="6"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>42</v>
-      </c>
+      <c r="B14" s="6"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>176</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>152</v>
-      </c>
+      <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>177</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>178</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>179</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>180</v>
-      </c>
-      <c r="B19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>181</v>
-      </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>182</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>183</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>184</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>185</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>186</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>187</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>188</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>189</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>190</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>174</v>
-      </c>
+      <c r="B16" s="6"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="7"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="8"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B21" s="10"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B22" s="10"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B23" s="10"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B24" s="10"/>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B25" s="10"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B26" s="10"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B27" s="10"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B28" s="10"/>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B29" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -3577,21 +3193,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C1" t="s">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="D1" t="s">
-        <v>192</v>
+        <v>127</v>
       </c>
       <c r="E1" t="s">
-        <v>193</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3599,17 +3215,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>192</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -3625,21 +3241,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C1" t="s">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="D1" t="s">
-        <v>195</v>
+        <v>130</v>
       </c>
       <c r="E1" t="s">
-        <v>196</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -3647,17 +3263,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>194</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>195</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -3679,175 +3295,175 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>197</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>246</v>
+        <v>181</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>216</v>
+        <v>151</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>247</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>217</v>
+        <v>152</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>199</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>215</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>248</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>221</v>
+        <v>156</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>203</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>222</v>
+        <v>157</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>202</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>223</v>
+        <v>158</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>224</v>
+        <v>159</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>225</v>
+        <v>160</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>249</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>226</v>
+        <v>161</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>213</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>227</v>
+        <v>162</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>209</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>228</v>
+        <v>163</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>204</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>229</v>
+        <v>164</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>200</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>250</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>231</v>
+        <v>166</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>214</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>205</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>233</v>
+        <v>168</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>210</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -3858,7 +3474,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAF9A1A-285A-4BA7-8832-B2D0F52F1F9B}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.125" customWidth="1"/>
@@ -3868,34 +3484,73 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
-        <v>277</v>
+        <v>206</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>278</v>
+        <v>207</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>280</v>
+        <v>209</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>281</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
-        <v>279</v>
+        <v>208</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>282</v>
+        <v>232</v>
       </c>
       <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
+      <c r="D4" s="20" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>237</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/Assets/CardLibrary/CardLibrary.xlsx
+++ b/Assets/CardLibrary/CardLibrary.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Poet\Assets\CardLibrary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3A6BCA-8F34-4596-8283-D4CCD6B4876A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2A8AEE-FE03-4CC3-8014-49C1A59883A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="826" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FullLibrary" sheetId="1" r:id="rId1"/>
     <sheet name="Raw_Choice" sheetId="5" r:id="rId2"/>
-    <sheet name="ForgeLibrary_Universal" sheetId="6" r:id="rId3"/>
-    <sheet name="ForgeLibrary_Nature" sheetId="8" r:id="rId4"/>
-    <sheet name="ForgeLibrary_Politics" sheetId="9" r:id="rId5"/>
-    <sheet name="ForgeLibrary_Emotion" sheetId="7" r:id="rId6"/>
-    <sheet name="Node" sheetId="10" r:id="rId7"/>
+    <sheet name="EventCard_Choices" sheetId="12" r:id="rId3"/>
+    <sheet name="ForgeLibrary_Universal" sheetId="6" r:id="rId4"/>
+    <sheet name="ForgeLibrary_Nature" sheetId="8" r:id="rId5"/>
+    <sheet name="ForgeLibrary_Politics" sheetId="9" r:id="rId6"/>
+    <sheet name="ForgeLibrary_Emotion" sheetId="7" r:id="rId7"/>
     <sheet name="DailyMission" sheetId="11" r:id="rId8"/>
+    <sheet name="Node" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="239">
   <si>
     <t>Index</t>
   </si>
@@ -2662,6 +2663,40 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BEFD67-833C-4C4B-AEEA-212EA8D4541D}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R18"/>
   <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3077,7 +3112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M29"/>
   <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3186,7 +3221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3234,7 +3269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3274,196 +3309,6 @@
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>131</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="14.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -3556,4 +3401,194 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="14.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>